--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée contient les traits d’identité du patient concerné par le document, connus par le producteur du document. Les informations présentes dans la métadonnée sourcePatientInfo ne doivent en aucun cas être réutilisées pour calculer un identifiant, ni être mises à jour après la soumission du document. 
-</t>
+    <t>Cette métadonnée contient les traits d’identité du patient concerné par le document, connus par le producteur du document. Les informations présentes dans la métadonnée sourcePatientInfo ne doivent en aucun cas être réutilisées pour calculer un identifiant, ni être mises à jour après la soumission du document.
+Cette métadonnée reprend la structure du segment PID (Patient Identification) défini par  HL7v2 et l'extension du profil IHE PAM, conformément aux spécifications  : 
+- [Extension française du profil IHE PAM](https://www.interopsante.org/publications)
+- [Prise en Charge de l'INS dans les volets du CI-SIS ](https://esante.gouv.fr/annexe-prise-en-charge-de-lins-dans-les-volets-du-ci-sis)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientInfo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="116">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID3</t>
+    <t>xdmSourcePatientInfo.pid3</t>
   </si>
   <si>
     <t>1</t>
@@ -263,71 +263,113 @@
 </t>
   </si>
   <si>
-    <t>Liste des identifiants du patient</t>
-  </si>
-  <si>
-    <t>xdmSourcePatientInfo.PID5</t>
+    <t>Liste des identifiants du patient.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid5</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Nom et prénoms du patient</t>
-  </si>
-  <si>
-    <t>xdmSourcePatientInfo.PID7</t>
-  </si>
-  <si>
-    <t>Date/heure de naissance du patient</t>
-  </si>
-  <si>
-    <t>xdmSourcePatientInfo.PID8</t>
-  </si>
-  <si>
-    <t>Sexe du patient</t>
-  </si>
-  <si>
-    <t>xdmSourcePatientInfo.PID11</t>
+    <t>Nom et prénoms du patient.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid7</t>
+  </si>
+  <si>
+    <t>Date/heure de naissance du patient. Obligatoire si l'INS est qualifié.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid8</t>
+  </si>
+  <si>
+    <t>Sexe du patient. Obligatoire si l'INS est qualifié.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid11</t>
   </si>
   <si>
     <t>Adresse du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID13</t>
+    <t>xdmSourcePatientInfo.pid13</t>
   </si>
   <si>
     <t>Téléphone de la résidence du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID14</t>
+    <t>xdmSourcePatientInfo.pid14</t>
   </si>
   <si>
     <t>Téléphone professionnel du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID15</t>
+    <t>xdmSourcePatientInfo.pid15</t>
   </si>
   <si>
     <t>Langue du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID16</t>
+    <t>xdmSourcePatientInfo.pid16</t>
   </si>
   <si>
     <t>Statut marital du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID18</t>
+    <t>xdmSourcePatientInfo.pid18</t>
   </si>
   <si>
     <t>Numéro de compte du patient</t>
   </si>
   <si>
-    <t>xdmSourcePatientInfo.PID21</t>
+    <t>xdmSourcePatientInfo.pid21</t>
   </si>
   <si>
     <t>Identifiant de la mère du patient</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid23</t>
+  </si>
+  <si>
+    <t>Lieu de naissance du patient. Obligatoire si l'INS est qualifié.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Indicateur de naissance multiple.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Ordre de naissance du patient.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date et heure de décès du patient.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientInfo.pid30</t>
+  </si>
+  <si>
+    <t>Indicateur de décès du patient.</t>
   </si>
 </sst>
 </file>
@@ -629,11 +671,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.42578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.23828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -642,7 +684,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.9765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.3359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -663,7 +705,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="23.42578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="23.23828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1979,6 +2021,506 @@
         <v>73</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
